--- a/data/partisympati_kön_inkomst.xlsx
+++ b/data/partisympati_kön_inkomst.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://svenskidrott-my.sharepoint.com/personal/william_lind_rfsisu_se/Documents/Dokument/GitHub/RF-SISU Uppland/sverige-i-siffror/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="271" documentId="11_B005A494D00B8E89AFD104F76C97BA2CAEE644AF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD07AD29-D3D3-41D2-A967-062F0319EF38}"/>
+  <xr:revisionPtr revIDLastSave="272" documentId="11_B005A494D00B8E89AFD104F76C97BA2CAEE644AF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD391885-770D-4BB5-BCBA-90229C791872}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1680" yWindow="3345" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad2" sheetId="6" r:id="rId1"/>
@@ -60,9 +60,6 @@
     <t>SD</t>
   </si>
   <si>
-    <t>övriga</t>
-  </si>
-  <si>
     <t>0-20 %</t>
   </si>
   <si>
@@ -94,6 +91,9 @@
   </si>
   <si>
     <t>Båda</t>
+  </si>
+  <si>
+    <t>Övriga</t>
   </si>
 </sst>
 </file>
@@ -647,7 +647,7 @@
     <tableColumn id="10" xr3:uid="{CDBC1C9E-0D9E-4934-AFC2-119DEE220773}" name="S" dataDxfId="3"/>
     <tableColumn id="11" xr3:uid="{F8007477-8574-4209-91B9-E54149C67789}" name="V" dataDxfId="2"/>
     <tableColumn id="12" xr3:uid="{B828649D-8021-4C93-AFD2-E7F3BE775DBA}" name="SD" dataDxfId="1"/>
-    <tableColumn id="13" xr3:uid="{F4B84927-9BAB-4EA2-8A35-ECD01CB1B655}" name="övriga" dataDxfId="0"/>
+    <tableColumn id="13" xr3:uid="{F4B84927-9BAB-4EA2-8A35-ECD01CB1B655}" name="Övriga" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -946,13 +946,13 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>16</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>17</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>0</v>
@@ -979,7 +979,7 @@
         <v>8</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -987,10 +987,10 @@
         <v>2008</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2">
         <v>21.7</v>
@@ -1025,10 +1025,10 @@
         <v>2009</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="1">
         <v>26.8</v>
@@ -1063,10 +1063,10 @@
         <v>2010</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2">
         <v>24.3</v>
@@ -1101,10 +1101,10 @@
         <v>2011</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" s="1">
         <v>28.4</v>
@@ -1139,10 +1139,10 @@
         <v>2012</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2">
         <v>23.3</v>
@@ -1177,10 +1177,10 @@
         <v>2013</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D7" s="1">
         <v>25.8</v>
@@ -1215,10 +1215,10 @@
         <v>2014</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2">
         <v>21.3</v>
@@ -1253,10 +1253,10 @@
         <v>2015</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D9" s="1">
         <v>28.3</v>
@@ -1291,10 +1291,10 @@
         <v>2016</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2">
         <v>24.4</v>
@@ -1329,10 +1329,10 @@
         <v>2017</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D11" s="1">
         <v>14.5</v>
@@ -1367,10 +1367,10 @@
         <v>2018</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2">
         <v>19.8</v>
@@ -1405,10 +1405,10 @@
         <v>2019</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D13" s="1">
         <v>21.2</v>
@@ -1443,10 +1443,10 @@
         <v>2020</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2">
         <v>23.5</v>
@@ -1481,10 +1481,10 @@
         <v>2021</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D15" s="1">
         <v>21.9</v>
@@ -1519,10 +1519,10 @@
         <v>2022</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2">
         <v>22.5</v>
@@ -1557,10 +1557,10 @@
         <v>2023</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D17" s="1">
         <v>18</v>
@@ -1595,10 +1595,10 @@
         <v>2024</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2">
         <v>19.5</v>
@@ -1633,10 +1633,10 @@
         <v>2025</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D19">
         <v>17.600000000000001</v>
@@ -1671,10 +1671,10 @@
         <v>2026</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D20" s="8">
         <v>20.2</v>
@@ -1709,10 +1709,10 @@
         <v>2008</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D21" s="2">
         <v>18.7</v>
@@ -1747,10 +1747,10 @@
         <v>2009</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D22" s="1">
         <v>22.3</v>
@@ -1785,10 +1785,10 @@
         <v>2010</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D23" s="2">
         <v>23.2</v>
@@ -1823,10 +1823,10 @@
         <v>2011</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D24" s="1">
         <v>20.7</v>
@@ -1861,10 +1861,10 @@
         <v>2012</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D25" s="2">
         <v>20.2</v>
@@ -1899,10 +1899,10 @@
         <v>2013</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D26" s="1">
         <v>19.600000000000001</v>
@@ -1937,10 +1937,10 @@
         <v>2014</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D27" s="2">
         <v>14.6</v>
@@ -1975,10 +1975,10 @@
         <v>2015</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D28" s="1">
         <v>15.5</v>
@@ -2013,10 +2013,10 @@
         <v>2016</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D29" s="2">
         <v>14.1</v>
@@ -2051,10 +2051,10 @@
         <v>2017</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D30" s="1">
         <v>12.1</v>
@@ -2089,10 +2089,10 @@
         <v>2018</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D31" s="2">
         <v>14.9</v>
@@ -2127,10 +2127,10 @@
         <v>2019</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D32" s="1">
         <v>11.5</v>
@@ -2165,10 +2165,10 @@
         <v>2020</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D33" s="2">
         <v>17.100000000000001</v>
@@ -2203,10 +2203,10 @@
         <v>2021</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D34" s="1">
         <v>13.3</v>
@@ -2241,10 +2241,10 @@
         <v>2022</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D35" s="2">
         <v>13.6</v>
@@ -2279,10 +2279,10 @@
         <v>2023</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D36" s="1">
         <v>11.7</v>
@@ -2317,10 +2317,10 @@
         <v>2024</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D37" s="2">
         <v>11.4</v>
@@ -2355,10 +2355,10 @@
         <v>2025</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D38">
         <v>10.6</v>
@@ -2393,10 +2393,10 @@
         <v>2026</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D39" s="8">
         <v>13.1</v>
@@ -2431,10 +2431,10 @@
         <v>2008</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D40" s="2">
         <v>15.7</v>
@@ -2469,10 +2469,10 @@
         <v>2009</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D41" s="1">
         <v>28.5</v>
@@ -2507,10 +2507,10 @@
         <v>2010</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D42" s="2">
         <v>25.6</v>
@@ -2545,10 +2545,10 @@
         <v>2011</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D43" s="1">
         <v>22.7</v>
@@ -2583,10 +2583,10 @@
         <v>2012</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D44" s="2">
         <v>20.100000000000001</v>
@@ -2621,10 +2621,10 @@
         <v>2013</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D45" s="1">
         <v>19.899999999999999</v>
@@ -2659,10 +2659,10 @@
         <v>2014</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D46" s="2">
         <v>13.7</v>
@@ -2697,10 +2697,10 @@
         <v>2015</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D47" s="1">
         <v>17.3</v>
@@ -2735,10 +2735,10 @@
         <v>2016</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D48" s="2">
         <v>18.3</v>
@@ -2773,10 +2773,10 @@
         <v>2017</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D49" s="1">
         <v>16.5</v>
@@ -2811,10 +2811,10 @@
         <v>2018</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D50" s="2">
         <v>19.399999999999999</v>
@@ -2849,10 +2849,10 @@
         <v>2019</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D51" s="1">
         <v>15.5</v>
@@ -2887,10 +2887,10 @@
         <v>2020</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D52" s="2">
         <v>15.5</v>
@@ -2925,10 +2925,10 @@
         <v>2021</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D53" s="1">
         <v>15.4</v>
@@ -2963,10 +2963,10 @@
         <v>2022</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D54" s="2">
         <v>15.7</v>
@@ -3001,10 +3001,10 @@
         <v>2023</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D55" s="1">
         <v>16</v>
@@ -3039,10 +3039,10 @@
         <v>2024</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D56" s="2">
         <v>17.2</v>
@@ -3077,10 +3077,10 @@
         <v>2025</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D57">
         <v>15.2</v>
@@ -3115,10 +3115,10 @@
         <v>2026</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D58" s="8">
         <v>14.8</v>
@@ -3153,10 +3153,10 @@
         <v>2008</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D59" s="2">
         <v>25.7</v>
@@ -3191,10 +3191,10 @@
         <v>2009</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D60" s="1">
         <v>29.4</v>
@@ -3229,10 +3229,10 @@
         <v>2010</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D61" s="2">
         <v>30.5</v>
@@ -3267,10 +3267,10 @@
         <v>2011</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D62" s="1">
         <v>32.799999999999997</v>
@@ -3305,10 +3305,10 @@
         <v>2012</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D63" s="2">
         <v>26.8</v>
@@ -3343,10 +3343,10 @@
         <v>2013</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D64" s="1">
         <v>27.9</v>
@@ -3381,10 +3381,10 @@
         <v>2014</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D65" s="2">
         <v>21</v>
@@ -3419,10 +3419,10 @@
         <v>2015</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D66" s="1">
         <v>24</v>
@@ -3457,10 +3457,10 @@
         <v>2016</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D67" s="2">
         <v>19.399999999999999</v>
@@ -3495,10 +3495,10 @@
         <v>2017</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D68" s="1">
         <v>18</v>
@@ -3533,10 +3533,10 @@
         <v>2018</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D69" s="2">
         <v>21.5</v>
@@ -3571,10 +3571,10 @@
         <v>2019</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D70" s="1">
         <v>20.399999999999999</v>
@@ -3609,10 +3609,10 @@
         <v>2020</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D71" s="2">
         <v>15.8</v>
@@ -3647,10 +3647,10 @@
         <v>2021</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D72" s="1">
         <v>19.2</v>
@@ -3685,10 +3685,10 @@
         <v>2022</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D73" s="2">
         <v>19.7</v>
@@ -3723,10 +3723,10 @@
         <v>2023</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D74" s="1">
         <v>17.8</v>
@@ -3761,10 +3761,10 @@
         <v>2024</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D75" s="2">
         <v>17.8</v>
@@ -3799,10 +3799,10 @@
         <v>2025</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D76">
         <v>18.7</v>
@@ -3837,10 +3837,10 @@
         <v>2026</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D77" s="8">
         <v>20.100000000000001</v>
@@ -3875,10 +3875,10 @@
         <v>2008</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D78" s="2">
         <v>39.200000000000003</v>
@@ -3913,10 +3913,10 @@
         <v>2009</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D79" s="1">
         <v>49.9</v>
@@ -3951,10 +3951,10 @@
         <v>2010</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D80" s="2">
         <v>52.9</v>
@@ -3989,10 +3989,10 @@
         <v>2011</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D81" s="1">
         <v>54.4</v>
@@ -4027,10 +4027,10 @@
         <v>2012</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D82" s="2">
         <v>48.7</v>
@@ -4065,10 +4065,10 @@
         <v>2013</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D83" s="1">
         <v>43</v>
@@ -4103,10 +4103,10 @@
         <v>2014</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D84" s="2">
         <v>39.6</v>
@@ -4141,10 +4141,10 @@
         <v>2015</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D85" s="1">
         <v>36.200000000000003</v>
@@ -4179,10 +4179,10 @@
         <v>2016</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D86" s="2">
         <v>39.799999999999997</v>
@@ -4217,10 +4217,10 @@
         <v>2017</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D87" s="1">
         <v>29.8</v>
@@ -4255,10 +4255,10 @@
         <v>2018</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D88" s="2">
         <v>36.5</v>
@@ -4293,10 +4293,10 @@
         <v>2019</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D89" s="1">
         <v>28.6</v>
@@ -4331,10 +4331,10 @@
         <v>2020</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D90" s="2">
         <v>35</v>
@@ -4369,10 +4369,10 @@
         <v>2021</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D91" s="1">
         <v>35</v>
@@ -4407,10 +4407,10 @@
         <v>2022</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D92" s="2">
         <v>31.9</v>
@@ -4445,10 +4445,10 @@
         <v>2023</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D93" s="1">
         <v>33.6</v>
@@ -4483,10 +4483,10 @@
         <v>2024</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D94" s="2">
         <v>32.5</v>
@@ -4521,10 +4521,10 @@
         <v>2025</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D95">
         <v>33.4</v>
@@ -4559,10 +4559,10 @@
         <v>2026</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D96" s="8">
         <v>28.3</v>
@@ -4597,10 +4597,10 @@
         <v>2008</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D97" s="2">
         <v>17.5</v>
@@ -4635,10 +4635,10 @@
         <v>2009</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D98" s="1">
         <v>22.6</v>
@@ -4673,10 +4673,10 @@
         <v>2010</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D99" s="2">
         <v>25</v>
@@ -4711,10 +4711,10 @@
         <v>2011</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D100" s="1">
         <v>22.2</v>
@@ -4749,10 +4749,10 @@
         <v>2012</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D101" s="2">
         <v>24.6</v>
@@ -4787,10 +4787,10 @@
         <v>2013</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D102" s="1">
         <v>20.9</v>
@@ -4825,10 +4825,10 @@
         <v>2014</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D103" s="2">
         <v>15.8</v>
@@ -4863,10 +4863,10 @@
         <v>2015</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D104" s="1">
         <v>22</v>
@@ -4901,10 +4901,10 @@
         <v>2016</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D105" s="2">
         <v>23</v>
@@ -4939,10 +4939,10 @@
         <v>2017</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D106" s="1">
         <v>15.7</v>
@@ -4977,10 +4977,10 @@
         <v>2018</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D107" s="2">
         <v>19.5</v>
@@ -5015,10 +5015,10 @@
         <v>2019</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D108" s="1">
         <v>12.2</v>
@@ -5053,10 +5053,10 @@
         <v>2020</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D109" s="2">
         <v>14.9</v>
@@ -5091,10 +5091,10 @@
         <v>2021</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D110" s="1">
         <v>15.3</v>
@@ -5129,10 +5129,10 @@
         <v>2022</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D111" s="2">
         <v>18.399999999999999</v>
@@ -5167,10 +5167,10 @@
         <v>2023</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D112" s="1">
         <v>14.9</v>
@@ -5205,10 +5205,10 @@
         <v>2024</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D113" s="2">
         <v>15.8</v>
@@ -5243,10 +5243,10 @@
         <v>2025</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D114">
         <v>15.9</v>
@@ -5281,10 +5281,10 @@
         <v>2026</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D115" s="8">
         <v>11.8</v>
@@ -5319,10 +5319,10 @@
         <v>2008</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D116" s="2">
         <v>19</v>
@@ -5357,10 +5357,10 @@
         <v>2009</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D117" s="1">
         <v>25</v>
@@ -5395,10 +5395,10 @@
         <v>2010</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D118" s="2">
         <v>25.2</v>
@@ -5433,10 +5433,10 @@
         <v>2011</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D119" s="1">
         <v>23.4</v>
@@ -5471,10 +5471,10 @@
         <v>2012</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D120" s="2">
         <v>19.5</v>
@@ -5509,10 +5509,10 @@
         <v>2013</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D121" s="1">
         <v>18</v>
@@ -5547,10 +5547,10 @@
         <v>2014</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D122" s="2">
         <v>15</v>
@@ -5585,10 +5585,10 @@
         <v>2015</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D123" s="1">
         <v>17.7</v>
@@ -5623,10 +5623,10 @@
         <v>2016</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D124" s="2">
         <v>19.5</v>
@@ -5661,10 +5661,10 @@
         <v>2017</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D125" s="1">
         <v>15.1</v>
@@ -5699,10 +5699,10 @@
         <v>2018</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D126" s="2">
         <v>15.6</v>
@@ -5737,10 +5737,10 @@
         <v>2019</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D127" s="1">
         <v>10.7</v>
@@ -5775,10 +5775,10 @@
         <v>2020</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D128" s="2">
         <v>16.5</v>
@@ -5813,10 +5813,10 @@
         <v>2021</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D129" s="1">
         <v>19</v>
@@ -5851,10 +5851,10 @@
         <v>2022</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D130" s="2">
         <v>16.3</v>
@@ -5889,10 +5889,10 @@
         <v>2023</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D131" s="1">
         <v>16.5</v>
@@ -5927,10 +5927,10 @@
         <v>2024</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D132" s="2">
         <v>15.2</v>
@@ -5965,10 +5965,10 @@
         <v>2025</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D133">
         <v>15.4</v>
@@ -6003,10 +6003,10 @@
         <v>2026</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D134" s="8">
         <v>12.7</v>
@@ -6041,10 +6041,10 @@
         <v>2008</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D135" s="2">
         <v>18.8</v>
@@ -6079,10 +6079,10 @@
         <v>2009</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D136" s="1">
         <v>25.1</v>
@@ -6117,10 +6117,10 @@
         <v>2010</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D137" s="2">
         <v>24.7</v>
@@ -6155,10 +6155,10 @@
         <v>2011</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D138" s="1">
         <v>28.9</v>
@@ -6193,10 +6193,10 @@
         <v>2012</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D139" s="2">
         <v>23</v>
@@ -6231,10 +6231,10 @@
         <v>2013</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D140" s="1">
         <v>21.7</v>
@@ -6269,10 +6269,10 @@
         <v>2014</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D141" s="2">
         <v>20.2</v>
@@ -6307,10 +6307,10 @@
         <v>2015</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D142" s="1">
         <v>22.6</v>
@@ -6345,10 +6345,10 @@
         <v>2016</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D143" s="2">
         <v>21.8</v>
@@ -6383,10 +6383,10 @@
         <v>2017</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D144" s="1">
         <v>15.9</v>
@@ -6421,10 +6421,10 @@
         <v>2018</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D145" s="2">
         <v>16.3</v>
@@ -6459,10 +6459,10 @@
         <v>2019</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D146" s="1">
         <v>14.2</v>
@@ -6497,10 +6497,10 @@
         <v>2020</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D147" s="2">
         <v>15.4</v>
@@ -6535,10 +6535,10 @@
         <v>2021</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D148" s="1">
         <v>19.5</v>
@@ -6573,10 +6573,10 @@
         <v>2022</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D149" s="2">
         <v>19.2</v>
@@ -6611,10 +6611,10 @@
         <v>2023</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D150" s="1">
         <v>18.8</v>
@@ -6649,10 +6649,10 @@
         <v>2024</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D151" s="2">
         <v>18</v>
@@ -6687,10 +6687,10 @@
         <v>2025</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D152">
         <v>16.2</v>
@@ -6725,10 +6725,10 @@
         <v>2026</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D153" s="8">
         <v>14.8</v>
@@ -6763,10 +6763,10 @@
         <v>2008</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D154" s="2">
         <v>23.3</v>
@@ -6801,10 +6801,10 @@
         <v>2009</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D155" s="1">
         <v>28.4</v>
@@ -6839,10 +6839,10 @@
         <v>2010</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D156" s="2">
         <v>30.6</v>
@@ -6877,10 +6877,10 @@
         <v>2011</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D157" s="1">
         <v>27.4</v>
@@ -6915,10 +6915,10 @@
         <v>2012</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D158" s="2">
         <v>28.6</v>
@@ -6953,10 +6953,10 @@
         <v>2013</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D159" s="1">
         <v>27.6</v>
@@ -6991,10 +6991,10 @@
         <v>2014</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D160" s="2">
         <v>22.2</v>
@@ -7029,10 +7029,10 @@
         <v>2015</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D161" s="1">
         <v>27.5</v>
@@ -7067,10 +7067,10 @@
         <v>2016</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D162" s="2">
         <v>23.8</v>
@@ -7105,10 +7105,10 @@
         <v>2017</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D163" s="1">
         <v>19.399999999999999</v>
@@ -7143,10 +7143,10 @@
         <v>2018</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D164" s="2">
         <v>20.8</v>
@@ -7181,10 +7181,10 @@
         <v>2019</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D165" s="1">
         <v>14.7</v>
@@ -7219,10 +7219,10 @@
         <v>2020</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D166" s="2">
         <v>22.1</v>
@@ -7257,10 +7257,10 @@
         <v>2021</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D167" s="1">
         <v>24.1</v>
@@ -7295,10 +7295,10 @@
         <v>2022</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D168" s="2">
         <v>23.7</v>
@@ -7333,10 +7333,10 @@
         <v>2023</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D169" s="1">
         <v>17.2</v>
@@ -7371,10 +7371,10 @@
         <v>2024</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D170" s="2">
         <v>20.7</v>
@@ -7409,10 +7409,10 @@
         <v>2025</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D171">
         <v>14.4</v>
@@ -7447,10 +7447,10 @@
         <v>2026</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D172" s="8">
         <v>19.5</v>
@@ -7485,10 +7485,10 @@
         <v>2008</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D173" s="2">
         <v>36.1</v>
@@ -7523,10 +7523,10 @@
         <v>2009</v>
       </c>
       <c r="B174" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D174" s="1">
         <v>43.1</v>
@@ -7561,10 +7561,10 @@
         <v>2010</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D175" s="2">
         <v>49.4</v>
@@ -7599,10 +7599,10 @@
         <v>2011</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D176" s="1">
         <v>44.7</v>
@@ -7637,10 +7637,10 @@
         <v>2012</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D177" s="2">
         <v>41.7</v>
@@ -7675,10 +7675,10 @@
         <v>2013</v>
       </c>
       <c r="B178" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D178" s="1">
         <v>40.9</v>
@@ -7713,10 +7713,10 @@
         <v>2014</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D179" s="2">
         <v>35.200000000000003</v>
@@ -7751,10 +7751,10 @@
         <v>2015</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D180" s="1">
         <v>43.5</v>
@@ -7789,10 +7789,10 @@
         <v>2016</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D181" s="2">
         <v>42.6</v>
@@ -7827,10 +7827,10 @@
         <v>2017</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D182" s="1">
         <v>31.1</v>
@@ -7865,10 +7865,10 @@
         <v>2018</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D183" s="2">
         <v>32.299999999999997</v>
@@ -7903,10 +7903,10 @@
         <v>2019</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C184" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D184" s="1">
         <v>23.3</v>
@@ -7941,10 +7941,10 @@
         <v>2020</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D185" s="2">
         <v>27.3</v>
@@ -7979,10 +7979,10 @@
         <v>2021</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D186" s="1">
         <v>33.4</v>
@@ -8017,10 +8017,10 @@
         <v>2022</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D187" s="2">
         <v>27.6</v>
@@ -8055,10 +8055,10 @@
         <v>2023</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C188" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D188" s="1">
         <v>26.1</v>
@@ -8093,10 +8093,10 @@
         <v>2024</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D189" s="2">
         <v>24.2</v>
@@ -8131,10 +8131,10 @@
         <v>2025</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C190" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D190">
         <v>24.8</v>
@@ -8169,10 +8169,10 @@
         <v>2026</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D191" s="8">
         <v>22.9</v>
@@ -8207,10 +8207,10 @@
         <v>2008</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D192" s="2">
         <v>19</v>
@@ -8245,10 +8245,10 @@
         <v>2009</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D193" s="1">
         <v>24.3</v>
@@ -8283,10 +8283,10 @@
         <v>2010</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D194" s="2">
         <v>24.8</v>
@@ -8321,10 +8321,10 @@
         <v>2011</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D195" s="1">
         <v>24.6</v>
@@ -8359,10 +8359,10 @@
         <v>2012</v>
       </c>
       <c r="B196" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D196" s="2">
         <v>24.1</v>
@@ -8397,10 +8397,10 @@
         <v>2013</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D197" s="1">
         <v>22.8</v>
@@ -8435,10 +8435,10 @@
         <v>2014</v>
       </c>
       <c r="B198" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D198" s="2">
         <v>17.8</v>
@@ -8473,10 +8473,10 @@
         <v>2015</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D199" s="1">
         <v>24.3</v>
@@ -8511,10 +8511,10 @@
         <v>2016</v>
       </c>
       <c r="B200" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D200" s="2">
         <v>23.5</v>
@@ -8549,10 +8549,10 @@
         <v>2017</v>
       </c>
       <c r="B201" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D201" s="1">
         <v>15.2</v>
@@ -8587,10 +8587,10 @@
         <v>2018</v>
       </c>
       <c r="B202" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D202" s="2">
         <v>19.600000000000001</v>
@@ -8625,10 +8625,10 @@
         <v>2019</v>
       </c>
       <c r="B203" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D203" s="1">
         <v>15.9</v>
@@ -8663,10 +8663,10 @@
         <v>2020</v>
       </c>
       <c r="B204" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D204" s="2">
         <v>18.3</v>
@@ -8701,10 +8701,10 @@
         <v>2021</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D205" s="1">
         <v>17.8</v>
@@ -8739,10 +8739,10 @@
         <v>2022</v>
       </c>
       <c r="B206" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D206" s="2">
         <v>19.899999999999999</v>
@@ -8777,10 +8777,10 @@
         <v>2023</v>
       </c>
       <c r="B207" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D207" s="1">
         <v>15.9</v>
@@ -8815,10 +8815,10 @@
         <v>2024</v>
       </c>
       <c r="B208" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D208" s="2">
         <v>17.3</v>
@@ -8853,10 +8853,10 @@
         <v>2025</v>
       </c>
       <c r="B209" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D209">
         <v>16.600000000000001</v>
@@ -8891,10 +8891,10 @@
         <v>2026</v>
       </c>
       <c r="B210" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D210" s="8">
         <v>15.4</v>
@@ -8929,10 +8929,10 @@
         <v>2008</v>
       </c>
       <c r="B211" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D211" s="2">
         <v>18.899999999999999</v>
@@ -8967,10 +8967,10 @@
         <v>2009</v>
       </c>
       <c r="B212" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D212" s="1">
         <v>24</v>
@@ -9005,10 +9005,10 @@
         <v>2010</v>
       </c>
       <c r="B213" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D213" s="2">
         <v>24.5</v>
@@ -9043,10 +9043,10 @@
         <v>2011</v>
       </c>
       <c r="B214" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D214" s="1">
         <v>22.4</v>
@@ -9081,10 +9081,10 @@
         <v>2012</v>
       </c>
       <c r="B215" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D215" s="2">
         <v>19.8</v>
@@ -9119,10 +9119,10 @@
         <v>2013</v>
       </c>
       <c r="B216" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D216" s="1">
         <v>18.600000000000001</v>
@@ -9157,10 +9157,10 @@
         <v>2014</v>
       </c>
       <c r="B217" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D217" s="2">
         <v>14.8</v>
@@ -9195,10 +9195,10 @@
         <v>2015</v>
       </c>
       <c r="B218" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D218" s="1">
         <v>16.8</v>
@@ -9233,10 +9233,10 @@
         <v>2016</v>
       </c>
       <c r="B219" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D219" s="2">
         <v>17.2</v>
@@ -9271,10 +9271,10 @@
         <v>2017</v>
       </c>
       <c r="B220" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D220" s="1">
         <v>13.9</v>
@@ -9309,10 +9309,10 @@
         <v>2018</v>
       </c>
       <c r="B221" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D221" s="2">
         <v>15.3</v>
@@ -9347,10 +9347,10 @@
         <v>2019</v>
       </c>
       <c r="B222" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D222" s="1">
         <v>11</v>
@@ -9385,10 +9385,10 @@
         <v>2020</v>
       </c>
       <c r="B223" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D223" s="2">
         <v>16.7</v>
@@ -9423,10 +9423,10 @@
         <v>2021</v>
       </c>
       <c r="B224" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D224" s="1">
         <v>16.600000000000001</v>
@@ -9461,10 +9461,10 @@
         <v>2022</v>
       </c>
       <c r="B225" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D225" s="2">
         <v>15.2</v>
@@ -9499,10 +9499,10 @@
         <v>2023</v>
       </c>
       <c r="B226" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D226" s="1">
         <v>14.6</v>
@@ -9537,10 +9537,10 @@
         <v>2024</v>
       </c>
       <c r="B227" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D227" s="2">
         <v>13.7</v>
@@ -9575,10 +9575,10 @@
         <v>2025</v>
       </c>
       <c r="B228" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D228">
         <v>13.5</v>
@@ -9613,10 +9613,10 @@
         <v>2026</v>
       </c>
       <c r="B229" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D229" s="8">
         <v>12.9</v>
@@ -9651,10 +9651,10 @@
         <v>2008</v>
       </c>
       <c r="B230" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D230" s="2">
         <v>17.399999999999999</v>
@@ -9689,10 +9689,10 @@
         <v>2009</v>
       </c>
       <c r="B231" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D231" s="1">
         <v>26.5</v>
@@ -9727,10 +9727,10 @@
         <v>2010</v>
       </c>
       <c r="B232" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D232" s="2">
         <v>25.1</v>
@@ -9765,10 +9765,10 @@
         <v>2011</v>
       </c>
       <c r="B233" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D233" s="1">
         <v>26.1</v>
@@ -9803,10 +9803,10 @@
         <v>2012</v>
       </c>
       <c r="B234" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D234" s="2">
         <v>21.7</v>
@@ -9841,10 +9841,10 @@
         <v>2013</v>
       </c>
       <c r="B235" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D235" s="1">
         <v>20.9</v>
@@ -9879,10 +9879,10 @@
         <v>2014</v>
       </c>
       <c r="B236" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D236" s="2">
         <v>17.3</v>
@@ -9917,10 +9917,10 @@
         <v>2015</v>
       </c>
       <c r="B237" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D237" s="1">
         <v>20.100000000000001</v>
@@ -9955,10 +9955,10 @@
         <v>2016</v>
       </c>
       <c r="B238" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D238" s="2">
         <v>20.2</v>
@@ -9993,10 +9993,10 @@
         <v>2017</v>
       </c>
       <c r="B239" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D239" s="1">
         <v>16.2</v>
@@ -10031,10 +10031,10 @@
         <v>2018</v>
       </c>
       <c r="B240" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D240" s="2">
         <v>17.8</v>
@@ -10069,10 +10069,10 @@
         <v>2019</v>
       </c>
       <c r="B241" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D241" s="1">
         <v>14.8</v>
@@ -10107,10 +10107,10 @@
         <v>2020</v>
       </c>
       <c r="B242" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D242" s="2">
         <v>15.5</v>
@@ -10145,10 +10145,10 @@
         <v>2021</v>
       </c>
       <c r="B243" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D243" s="1">
         <v>17.600000000000001</v>
@@ -10183,10 +10183,10 @@
         <v>2022</v>
       </c>
       <c r="B244" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D244" s="2">
         <v>17.600000000000001</v>
@@ -10221,10 +10221,10 @@
         <v>2023</v>
       </c>
       <c r="B245" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D245" s="1">
         <v>17.5</v>
@@ -10259,10 +10259,10 @@
         <v>2024</v>
       </c>
       <c r="B246" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D246" s="2">
         <v>17.600000000000001</v>
@@ -10297,10 +10297,10 @@
         <v>2025</v>
       </c>
       <c r="B247" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D247">
         <v>15.7</v>
@@ -10335,10 +10335,10 @@
         <v>2026</v>
       </c>
       <c r="B248" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D248" s="8">
         <v>14.8</v>
@@ -10373,10 +10373,10 @@
         <v>2008</v>
       </c>
       <c r="B249" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C249" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D249" s="2">
         <v>24.6</v>
@@ -10411,10 +10411,10 @@
         <v>2009</v>
       </c>
       <c r="B250" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C250" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D250" s="1">
         <v>29</v>
@@ -10449,10 +10449,10 @@
         <v>2010</v>
       </c>
       <c r="B251" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C251" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D251" s="2">
         <v>30.5</v>
@@ -10487,10 +10487,10 @@
         <v>2011</v>
       </c>
       <c r="B252" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C252" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D252" s="1">
         <v>30.1</v>
@@ -10525,10 +10525,10 @@
         <v>2012</v>
       </c>
       <c r="B253" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C253" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D253" s="2">
         <v>27.6</v>
@@ -10563,10 +10563,10 @@
         <v>2013</v>
       </c>
       <c r="B254" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C254" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D254" s="1">
         <v>27.7</v>
@@ -10601,10 +10601,10 @@
         <v>2014</v>
       </c>
       <c r="B255" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C255" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D255" s="2">
         <v>21.5</v>
@@ -10639,10 +10639,10 @@
         <v>2015</v>
       </c>
       <c r="B256" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C256" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D256" s="1">
         <v>25.6</v>
@@ -10677,10 +10677,10 @@
         <v>2016</v>
       </c>
       <c r="B257" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C257" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D257" s="2">
         <v>21.4</v>
@@ -10715,10 +10715,10 @@
         <v>2017</v>
       </c>
       <c r="B258" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C258" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D258" s="1">
         <v>18.7</v>
@@ -10753,10 +10753,10 @@
         <v>2018</v>
       </c>
       <c r="B259" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C259" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D259" s="2">
         <v>21.1</v>
@@ -10791,10 +10791,10 @@
         <v>2019</v>
       </c>
       <c r="B260" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C260" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D260" s="1">
         <v>17.899999999999999</v>
@@ -10829,10 +10829,10 @@
         <v>2020</v>
       </c>
       <c r="B261" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C261" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D261" s="2">
         <v>18.7</v>
@@ -10867,10 +10867,10 @@
         <v>2021</v>
       </c>
       <c r="B262" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C262" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D262" s="1">
         <v>21.5</v>
@@ -10905,10 +10905,10 @@
         <v>2022</v>
       </c>
       <c r="B263" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C263" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D263" s="2">
         <v>21.5</v>
@@ -10943,10 +10943,10 @@
         <v>2023</v>
       </c>
       <c r="B264" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C264" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D264" s="1">
         <v>17.5</v>
@@ -10981,10 +10981,10 @@
         <v>2024</v>
       </c>
       <c r="B265" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C265" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D265" s="2">
         <v>19.100000000000001</v>
@@ -11019,10 +11019,10 @@
         <v>2025</v>
       </c>
       <c r="B266" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C266" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D266">
         <v>16.8</v>
@@ -11057,10 +11057,10 @@
         <v>2026</v>
       </c>
       <c r="B267" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C267" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D267" s="8">
         <v>19.8</v>
@@ -11095,10 +11095,10 @@
         <v>2008</v>
       </c>
       <c r="B268" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C268" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D268" s="2">
         <v>38.299999999999997</v>
@@ -11133,10 +11133,10 @@
         <v>2009</v>
       </c>
       <c r="B269" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C269" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D269" s="1">
         <v>47.9</v>
@@ -11171,10 +11171,10 @@
         <v>2010</v>
       </c>
       <c r="B270" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C270" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D270" s="2">
         <v>51.9</v>
@@ -11209,10 +11209,10 @@
         <v>2011</v>
       </c>
       <c r="B271" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C271" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D271" s="1">
         <v>51.4</v>
@@ -11247,10 +11247,10 @@
         <v>2012</v>
       </c>
       <c r="B272" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C272" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D272" s="2">
         <v>46.5</v>
@@ -11285,10 +11285,10 @@
         <v>2013</v>
       </c>
       <c r="B273" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C273" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D273" s="1">
         <v>42.4</v>
@@ -11323,10 +11323,10 @@
         <v>2014</v>
       </c>
       <c r="B274" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C274" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D274" s="2">
         <v>38.200000000000003</v>
@@ -11361,10 +11361,10 @@
         <v>2015</v>
       </c>
       <c r="B275" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C275" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D275" s="1">
         <v>38.700000000000003</v>
@@ -11399,10 +11399,10 @@
         <v>2016</v>
       </c>
       <c r="B276" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C276" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D276" s="2">
         <v>40.700000000000003</v>
@@ -11437,10 +11437,10 @@
         <v>2017</v>
       </c>
       <c r="B277" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C277" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D277" s="1">
         <v>30.2</v>
@@ -11475,10 +11475,10 @@
         <v>2018</v>
       </c>
       <c r="B278" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C278" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D278" s="2">
         <v>35</v>
@@ -11513,10 +11513,10 @@
         <v>2019</v>
       </c>
       <c r="B279" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C279" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D279" s="1">
         <v>26.6</v>
@@ -11551,10 +11551,10 @@
         <v>2020</v>
       </c>
       <c r="B280" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C280" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D280" s="2">
         <v>32.4</v>
@@ -11589,10 +11589,10 @@
         <v>2021</v>
       </c>
       <c r="B281" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C281" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D281" s="1">
         <v>34.5</v>
@@ -11627,10 +11627,10 @@
         <v>2022</v>
       </c>
       <c r="B282" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C282" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D282" s="2">
         <v>30.3</v>
@@ -11665,10 +11665,10 @@
         <v>2023</v>
       </c>
       <c r="B283" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C283" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D283" s="1">
         <v>30.9</v>
@@ -11703,10 +11703,10 @@
         <v>2024</v>
       </c>
       <c r="B284" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C284" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D284" s="2">
         <v>29.5</v>
@@ -11741,10 +11741,10 @@
         <v>2025</v>
       </c>
       <c r="B285" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C285" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D285">
         <v>30.3</v>
@@ -11779,10 +11779,10 @@
         <v>2026</v>
       </c>
       <c r="B286" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C286" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D286" s="8">
         <v>26.2</v>
